--- a/src/test/resources/TestData/AVSVer_TestData.xlsx
+++ b/src/test/resources/TestData/AVSVer_TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaveri.Bedar\git\AVS-QUAL-FLOW\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51C799D-31A7-4795-8B6F-F2DE1DCB2C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E29945-A6B8-477D-BC2E-C1DE20AA1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVS_Ver" sheetId="1" r:id="rId1"/>
@@ -52,10 +52,10 @@
     <t>AVS_Caliberation</t>
   </si>
   <si>
-    <t>192.168.1.2</t>
-  </si>
-  <si>
-    <t>IP 192.168.1.2</t>
+    <t>10.17.18.222</t>
+  </si>
+  <si>
+    <t>IP 10.17.18.222</t>
   </si>
 </sst>
 </file>
@@ -401,16 +401,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -452,12 +452,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{074AFF5F-76E6-4981-97A0-D1B7A899F69F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
